--- a/Assets/Excel/Portia/PortiaConfig.xlsx
+++ b/Assets/Excel/Portia/PortiaConfig.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\peizhi\新建文件夹\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamejam\ceshi\Assets\Excel\Portia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD910631-A111-44EE-8147-4768727FE783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D049FFFF-C957-4A1F-A8D5-B6749F233455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="83">
   <si>
     <t>建筑唯一ID</t>
   </si>
@@ -325,6 +325,18 @@
   </si>
   <si>
     <t>map</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>锡矿石</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落数量</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>num</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1465,7 +1477,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -1570,26 +1582,23 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>301</v>
+        <v>205</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10">
+        <v>7</v>
+      </c>
+      <c r="D10">
         <v>10</v>
       </c>
       <c r="E10">
@@ -1598,21 +1607,24 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>401</v>
+        <v>302</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>76</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -1620,10 +1632,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13">
         <v>4</v>
@@ -1631,21 +1643,21 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>501</v>
+        <v>403</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -1653,10 +1665,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -1664,12 +1676,23 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
+        <v>503</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
         <v>505</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>52</v>
       </c>
-      <c r="E17">
+      <c r="E18">
         <v>2</v>
       </c>
     </row>
@@ -1908,10 +1931,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>61</v>
       </c>
@@ -1928,13 +1951,16 @@
         <v>72</v>
       </c>
       <c r="F1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" t="s">
         <v>73</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -1951,13 +1977,16 @@
         <v>74</v>
       </c>
       <c r="F2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" t="s">
         <v>75</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>62</v>
       </c>
@@ -1974,10 +2003,13 @@
         <v>201</v>
       </c>
       <c r="F3">
+        <v>20</v>
+      </c>
+      <c r="G3">
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -1993,11 +2025,14 @@
       <c r="E4" s="1">
         <v>202204</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -2011,13 +2046,16 @@
         <v>50</v>
       </c>
       <c r="E5" s="1">
-        <v>202203</v>
-      </c>
-      <c r="F5" t="s">
+        <v>205203</v>
+      </c>
+      <c r="F5" s="1">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -2031,10 +2069,13 @@
         <v>201</v>
       </c>
       <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -2048,10 +2089,13 @@
         <v>202</v>
       </c>
       <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -2065,6 +2109,9 @@
         <v>302</v>
       </c>
       <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
         <v>100</v>
       </c>
     </row>

--- a/Assets/Excel/Portia/PortiaConfig.xlsx
+++ b/Assets/Excel/Portia/PortiaConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamejam\ceshi\Assets\Excel\Portia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D049FFFF-C957-4A1F-A8D5-B6749F233455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4B529D-E4DE-4394-BFEA-A5D0D6605005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="88">
   <si>
     <t>建筑唯一ID</t>
   </si>
@@ -337,6 +337,26 @@
   </si>
   <si>
     <t>num</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁锅</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>青铜锭</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>烹饪锅</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,6</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1312,7 +1332,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.25" bestFit="1" customWidth="1"/>
@@ -1469,6 +1489,32 @@
         <v>403</v>
       </c>
     </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>20</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>404</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1477,7 +1523,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -1654,21 +1700,21 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>501</v>
+        <v>404</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -1676,10 +1722,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -1687,12 +1733,45 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18">
+        <v>503</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
         <v>505</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>52</v>
       </c>
-      <c r="E18">
+      <c r="E19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>506</v>
+      </c>
+      <c r="B20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>507</v>
+      </c>
+      <c r="B21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21">
         <v>2</v>
       </c>
     </row>
@@ -1704,7 +1783,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.75" bestFit="1" customWidth="1"/>
@@ -1920,6 +1999,84 @@
         <v>3</v>
       </c>
       <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9">
+        <v>503</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>506</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="1">
+        <v>203205</v>
+      </c>
+      <c r="D10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10">
+        <v>507</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="1">
+        <v>506501202</v>
+      </c>
+      <c r="D11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11">
+        <v>404</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Excel/Portia/PortiaConfig.xlsx
+++ b/Assets/Excel/Portia/PortiaConfig.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamejam\ceshi\Assets\Excel\Portia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4B529D-E4DE-4394-BFEA-A5D0D6605005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734C7E5F-BF27-480F-A967-36A5F69C7D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Machines" sheetId="1" r:id="rId1"/>
     <sheet name="item" sheetId="2" r:id="rId2"/>
     <sheet name="synthesis" sheetId="5" r:id="rId3"/>
     <sheet name="mapbuilding" sheetId="3" r:id="rId4"/>
+    <sheet name="mapbuildingXYZ" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="116">
   <si>
     <t>建筑唯一ID</t>
   </si>
@@ -357,6 +358,118 @@
   </si>
   <si>
     <t>1,2,6</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>X坐标</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y坐标</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z坐标</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源id</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>mapbuildingid</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>234.267f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>44.6f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>-121.245f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>名字</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>45.516f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>-125.482f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>239.037f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>43.688f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">-129.958f </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>226.346f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>42.862f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">-140.961f </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>219.252f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>43.84f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>-138.315f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>229.986f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>42.183f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>-143.837f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>243.557f</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -950,11 +1063,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2088,188 +2204,335 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>61</v>
       </c>
       <c r="B1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" t="s">
         <v>67</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>70</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>71</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>72</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>81</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>73</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>61</v>
       </c>
       <c r="B2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" t="s">
         <v>68</v>
       </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3">
+        <v>101</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>201</v>
+      </c>
+      <c r="G3">
+        <v>20</v>
+      </c>
+      <c r="H3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4">
+        <v>102</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1">
+        <v>202204</v>
+      </c>
+      <c r="G4" s="1">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5">
+        <v>102</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" s="1">
+        <v>205203</v>
+      </c>
+      <c r="G5" s="1">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>201</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>202</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>302</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{842578EF-BAAD-4A38-9BF7-3C5DB974AEE0}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" t="s">
+        <v>92</v>
+      </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3">
+        <v>96</v>
+      </c>
+      <c r="B3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" t="s">
         <v>101</v>
       </c>
-      <c r="C3">
+      <c r="C4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5">
         <v>3</v>
       </c>
-      <c r="D3">
-        <v>50</v>
-      </c>
-      <c r="E3">
-        <v>201</v>
-      </c>
-      <c r="F3">
-        <v>20</v>
-      </c>
-      <c r="G3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4">
-        <v>102</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>50</v>
-      </c>
-      <c r="E4" s="1">
-        <v>202204</v>
-      </c>
-      <c r="F4" s="1">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5">
-        <v>102</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>50</v>
-      </c>
-      <c r="E5" s="1">
-        <v>205203</v>
-      </c>
-      <c r="F5" s="1">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
+        <v>106</v>
+      </c>
+      <c r="B6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="D6">
-        <v>50</v>
-      </c>
-      <c r="E6">
-        <v>201</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
+        <v>109</v>
+      </c>
+      <c r="B7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="D7">
-        <v>50</v>
-      </c>
-      <c r="E7">
-        <v>202</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
+        <v>112</v>
+      </c>
+      <c r="B8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="D8">
-        <v>50</v>
-      </c>
-      <c r="E8">
-        <v>302</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>100</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/Portia/PortiaConfig.xlsx
+++ b/Assets/Excel/Portia/PortiaConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamejam\ceshi\Assets\Excel\Portia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734C7E5F-BF27-480F-A967-36A5F69C7D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41FB2A06-30B3-4C68-A896-3EF8E528A370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Machines" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="149">
   <si>
     <t>建筑唯一ID</t>
   </si>
@@ -201,10 +201,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>每一点容量维持时间</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>石砖</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -470,6 +466,125 @@
   </si>
   <si>
     <t>243.557f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>模型</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>cityLevel_Open</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\Model\home\HomeItem_Grinder1.prefab</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\Model\home\HomeItem_Cutting2.prefab</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\Model\home\HomeItem_CookMachine.prefab</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\Model\home\Factory_lv1.prefab</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>iconPath</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>prefabPath</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>图标</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_Axe.png</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_hoe_steel</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_huYangMu</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_stone_009</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_stone_007</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_crystal</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_stone_011</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_mushroom01</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_machine_furnace02</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_machine_sawing</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_machine_cookingBench</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_stone_002</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_productionLine_WoodCompositeBoard</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_metal_004</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_home_wateredFloor</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_products_steelPan</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_metal_006</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\Model\itemmall\comparegame\ItemCom_Axe.prefab</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\Model\itemmall\Item_hoe_lv1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\Model\GameObject\tree007_7</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\Model\interactive\stone\stone_interactive_01</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\Model\interactive\stone\stone_interactive_color_01</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\Model\plant\stone_mini</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\Model\itemmall\ItemMall_mushroom</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每一点容量维持时间/秒</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -477,7 +592,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -637,6 +752,22 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -1063,7 +1194,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1071,6 +1202,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1448,7 +1591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.25" bestFit="1" customWidth="1"/>
@@ -1457,7 +1600,7 @@
     <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1477,7 +1620,7 @@
         <v>47</v>
       </c>
       <c r="G1" t="s">
-        <v>48</v>
+        <v>148</v>
       </c>
       <c r="H1" t="s">
         <v>35</v>
@@ -1486,10 +1629,13 @@
         <v>23</v>
       </c>
       <c r="J1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="K1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1518,10 +1664,13 @@
         <v>31</v>
       </c>
       <c r="J2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+      <c r="K2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1540,6 +1689,9 @@
       <c r="F3">
         <v>10</v>
       </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
       <c r="H3">
         <v>20</v>
       </c>
@@ -1549,8 +1701,11 @@
       <c r="J3">
         <v>401</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K3" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1569,6 +1724,9 @@
       <c r="F4">
         <v>10</v>
       </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
       <c r="H4">
         <v>20</v>
       </c>
@@ -1578,8 +1736,11 @@
       <c r="J4">
         <v>402</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K4" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1595,6 +1756,9 @@
       <c r="F5">
         <v>10</v>
       </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
       <c r="H5">
         <v>20</v>
       </c>
@@ -1604,13 +1768,16 @@
       <c r="J5">
         <v>403</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K5" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1621,6 +1788,9 @@
       <c r="F6">
         <v>10</v>
       </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
       <c r="H6">
         <v>20</v>
       </c>
@@ -1629,6 +1799,9 @@
       </c>
       <c r="J6">
         <v>404</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1639,10 +1812,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -1658,8 +1831,14 @@
       <c r="E1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1675,8 +1854,14 @@
       <c r="E2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>101</v>
       </c>
@@ -1686,8 +1871,15 @@
       <c r="E3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>102</v>
       </c>
@@ -1697,8 +1889,15 @@
       <c r="E4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>201</v>
       </c>
@@ -1708,8 +1907,12 @@
       <c r="E5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>202</v>
       </c>
@@ -1719,8 +1922,12 @@
       <c r="E6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6" t="s">
+        <v>127</v>
+      </c>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>203</v>
       </c>
@@ -1730,8 +1937,12 @@
       <c r="E7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F7" t="s">
+        <v>128</v>
+      </c>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>204</v>
       </c>
@@ -1741,19 +1952,27 @@
       <c r="E8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F8" t="s">
+        <v>129</v>
+      </c>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>205</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F9" t="s">
+        <v>130</v>
+      </c>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>301</v>
       </c>
@@ -1766,13 +1985,14 @@
       <c r="E10">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>302</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1780,8 +2000,12 @@
       <c r="E11">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F11" t="s">
+        <v>131</v>
+      </c>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>401</v>
       </c>
@@ -1791,8 +2015,9 @@
       <c r="E12">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>402</v>
       </c>
@@ -1802,8 +2027,12 @@
       <c r="E13">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F13" t="s">
+        <v>132</v>
+      </c>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>403</v>
       </c>
@@ -1813,83 +2042,115 @@
       <c r="E14">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F14" t="s">
+        <v>133</v>
+      </c>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>404</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E15">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F15" t="s">
+        <v>134</v>
+      </c>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>501</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F16" t="s">
+        <v>135</v>
+      </c>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>502</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F17" t="s">
+        <v>136</v>
+      </c>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>503</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F18" t="s">
+        <v>137</v>
+      </c>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>505</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F19" t="s">
+        <v>138</v>
+      </c>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>506</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F20" t="s">
+        <v>139</v>
+      </c>
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>507</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
+      <c r="F21" t="s">
+        <v>140</v>
+      </c>
+      <c r="J21" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
@@ -1930,10 +2191,10 @@
         <v>13</v>
       </c>
       <c r="G1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -1956,10 +2217,10 @@
         <v>18</v>
       </c>
       <c r="G2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" t="s">
         <v>58</v>
-      </c>
-      <c r="H2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -1967,7 +2228,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C3">
         <v>202</v>
@@ -1993,7 +2254,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>201</v>
@@ -2019,7 +2280,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>203</v>
@@ -2045,7 +2306,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>503</v>
@@ -2077,7 +2338,7 @@
         <v>201202</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>402</v>
@@ -2100,10 +2361,10 @@
         <v>33</v>
       </c>
       <c r="C8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" t="s">
         <v>56</v>
-      </c>
-      <c r="D8" t="s">
-        <v>57</v>
       </c>
       <c r="E8">
         <v>403</v>
@@ -2123,7 +2384,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9">
         <v>503</v>
@@ -2149,13 +2410,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" s="1">
         <v>203205</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E10">
         <v>507</v>
@@ -2175,13 +2436,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" s="1">
         <v>506501202</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E11">
         <v>404</v>
@@ -2204,73 +2465,79 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>61</v>
-      </c>
-      <c r="B1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H2" t="s">
-        <v>75</v>
-      </c>
-      <c r="I2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>62</v>
       </c>
       <c r="C3">
         <v>101</v>
@@ -2290,8 +2557,11 @@
       <c r="H3">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J3" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2314,15 +2584,18 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C5">
         <v>102</v>
@@ -2340,15 +2613,18 @@
         <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -2365,13 +2641,14 @@
       <c r="H6">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2388,13 +2665,16 @@
       <c r="H7">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J7" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2410,6 +2690,9 @@
       </c>
       <c r="H8">
         <v>100</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -2425,41 +2708,41 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>89</v>
       </c>
-      <c r="C1" t="s">
-        <v>90</v>
-      </c>
       <c r="D1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" t="s">
         <v>91</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>92</v>
       </c>
-      <c r="C2" t="s">
-        <v>93</v>
-      </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" t="s">
         <v>96</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2467,13 +2750,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -2481,13 +2764,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -2495,13 +2778,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" t="s">
         <v>106</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -2509,13 +2792,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" t="s">
         <v>109</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -2523,13 +2806,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B8" t="s">
         <v>112</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="D8">
         <v>6</v>

--- a/Assets/Excel/Portia/PortiaConfig.xlsx
+++ b/Assets/Excel/Portia/PortiaConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamejam\ceshi\Assets\Excel\Portia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41FB2A06-30B3-4C68-A896-3EF8E528A370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D060E0-9DFB-4E52-91E1-1D949200633F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Machines" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="150">
   <si>
     <t>建筑唯一ID</t>
   </si>
@@ -585,6 +585,10 @@
   </si>
   <si>
     <t>每一点容量维持时间/秒</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\Model\npcobjects\Toby_Stick</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2641,7 +2645,9 @@
       <c r="H6">
         <v>100</v>
       </c>
-      <c r="J6" s="6"/>
+      <c r="J6" s="6" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">

--- a/Assets/Excel/Portia/PortiaConfig.xlsx
+++ b/Assets/Excel/Portia/PortiaConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamejam\ceshi\Assets\Excel\Portia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D060E0-9DFB-4E52-91E1-1D949200633F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F06938DB-D8EC-40BF-916A-7DEC4805940C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Machines" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="151">
   <si>
     <t>建筑唯一ID</t>
   </si>
@@ -409,18 +409,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>45.516f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>-125.482f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>239.037f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>43.688f</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -589,6 +577,22 @@
   </si>
   <si>
     <t>Assets\Games\GameJam\assets\Model\npcobjects\Toby_Stick</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>237.558f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>44.161f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>-126.931f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_craftTable01</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1624,7 +1628,7 @@
         <v>47</v>
       </c>
       <c r="G1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H1" t="s">
         <v>35</v>
@@ -1636,7 +1640,7 @@
         <v>54</v>
       </c>
       <c r="K1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -1671,7 +1675,7 @@
         <v>53</v>
       </c>
       <c r="K2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -1706,7 +1710,7 @@
         <v>401</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -1741,7 +1745,7 @@
         <v>402</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -1773,7 +1777,7 @@
         <v>403</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -1805,7 +1809,7 @@
         <v>404</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1836,10 +1840,10 @@
         <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -1859,10 +1863,10 @@
         <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1876,10 +1880,10 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -1894,10 +1898,10 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="J4" s="3"/>
     </row>
@@ -1912,7 +1916,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -1927,7 +1931,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -1942,7 +1946,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -1957,7 +1961,7 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -1972,7 +1976,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -2005,7 +2009,7 @@
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="J11" s="3"/>
     </row>
@@ -2019,6 +2023,9 @@
       <c r="E12">
         <v>4</v>
       </c>
+      <c r="F12" t="s">
+        <v>150</v>
+      </c>
       <c r="J12" s="4"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -2032,7 +2039,7 @@
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J13" s="3"/>
     </row>
@@ -2047,7 +2054,7 @@
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J14" s="3"/>
     </row>
@@ -2062,7 +2069,7 @@
         <v>4</v>
       </c>
       <c r="F15" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="J15" s="3"/>
     </row>
@@ -2077,7 +2084,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J16" s="3"/>
     </row>
@@ -2092,7 +2099,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J17" s="3"/>
     </row>
@@ -2107,7 +2114,7 @@
         <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3"/>
     </row>
@@ -2122,7 +2129,7 @@
         <v>2</v>
       </c>
       <c r="F19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="J19" s="3"/>
     </row>
@@ -2137,7 +2144,7 @@
         <v>2</v>
       </c>
       <c r="F20" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="J20" s="3"/>
     </row>
@@ -2152,7 +2159,7 @@
         <v>2</v>
       </c>
       <c r="F21" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J21" s="3"/>
     </row>
@@ -2501,7 +2508,7 @@
         <v>77</v>
       </c>
       <c r="J1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -2533,7 +2540,7 @@
         <v>78</v>
       </c>
       <c r="J2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -2562,7 +2569,7 @@
         <v>100</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -2591,7 +2598,7 @@
         <v>76</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -2620,7 +2627,7 @@
         <v>76</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -2646,7 +2653,7 @@
         <v>100</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -2672,7 +2679,7 @@
         <v>100</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -2698,7 +2705,7 @@
         <v>100</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2756,13 +2763,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -2770,13 +2777,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -2784,13 +2791,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -2798,13 +2805,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -2812,13 +2819,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D8">
         <v>6</v>

--- a/Assets/Excel/Portia/PortiaConfig.xlsx
+++ b/Assets/Excel/Portia/PortiaConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamejam\ceshi\Assets\Excel\Portia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F06938DB-D8EC-40BF-916A-7DEC4805940C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CF934F-D375-40F6-9999-B142CAD888F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Machines" sheetId="1" r:id="rId1"/>
@@ -389,18 +389,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>234.267f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>44.6f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>-121.245f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>名字</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -409,54 +397,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>43.688f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">-129.958f </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>226.346f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>42.862f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">-140.961f </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>219.252f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>43.84f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>-138.315f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>229.986f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>42.183f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>-143.837f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>243.557f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>模型</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -580,19 +520,79 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>237.558f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>44.161f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>-126.931f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_craftTable01</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>252.193f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>42.088f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>-138.995f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>247.474f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>42.961f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>-134.062f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>242.922f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>43.615f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">-130.524f </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>228.722f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>41.963f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>-146.408f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>236.521f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>40.968f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">-150.503f </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>244.609f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>39.948f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>-154.462f</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1628,7 +1628,7 @@
         <v>47</v>
       </c>
       <c r="G1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="H1" t="s">
         <v>35</v>
@@ -1640,7 +1640,7 @@
         <v>54</v>
       </c>
       <c r="K1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -1675,7 +1675,7 @@
         <v>53</v>
       </c>
       <c r="K2" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -1710,7 +1710,7 @@
         <v>401</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -1745,7 +1745,7 @@
         <v>402</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -1777,7 +1777,7 @@
         <v>403</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -1809,7 +1809,7 @@
         <v>404</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1840,10 +1840,10 @@
         <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="G1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -1863,10 +1863,10 @@
         <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G2" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1880,10 +1880,10 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -1898,10 +1898,10 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="J4" s="3"/>
     </row>
@@ -1916,7 +1916,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -1931,7 +1931,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -1946,7 +1946,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -1961,7 +1961,7 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -1976,7 +1976,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -2009,7 +2009,7 @@
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="J11" s="3"/>
     </row>
@@ -2024,7 +2024,7 @@
         <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="J12" s="4"/>
     </row>
@@ -2039,7 +2039,7 @@
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="J13" s="3"/>
     </row>
@@ -2054,7 +2054,7 @@
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="J14" s="3"/>
     </row>
@@ -2069,7 +2069,7 @@
         <v>4</v>
       </c>
       <c r="F15" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="J15" s="3"/>
     </row>
@@ -2084,7 +2084,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="J16" s="3"/>
     </row>
@@ -2099,7 +2099,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="J17" s="3"/>
     </row>
@@ -2114,7 +2114,7 @@
         <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="J18" s="3"/>
     </row>
@@ -2129,7 +2129,7 @@
         <v>2</v>
       </c>
       <c r="F19" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="J19" s="3"/>
     </row>
@@ -2144,7 +2144,7 @@
         <v>2</v>
       </c>
       <c r="F20" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="J20" s="3"/>
     </row>
@@ -2159,7 +2159,7 @@
         <v>2</v>
       </c>
       <c r="F21" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="J21" s="3"/>
     </row>
@@ -2484,7 +2484,7 @@
         <v>60</v>
       </c>
       <c r="B1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s">
         <v>66</v>
@@ -2508,7 +2508,7 @@
         <v>77</v>
       </c>
       <c r="J1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -2516,7 +2516,7 @@
         <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
         <v>67</v>
@@ -2540,7 +2540,7 @@
         <v>78</v>
       </c>
       <c r="J2" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -2569,7 +2569,7 @@
         <v>100</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -2598,7 +2598,7 @@
         <v>76</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -2627,7 +2627,7 @@
         <v>76</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -2653,7 +2653,7 @@
         <v>100</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -2679,7 +2679,7 @@
         <v>100</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -2705,7 +2705,7 @@
         <v>100</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2749,13 +2749,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>97</v>
+        <v>150</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2763,13 +2763,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="B4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -2777,13 +2777,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -2791,13 +2791,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -2805,13 +2805,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -2819,13 +2819,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="D8">
         <v>6</v>

--- a/Assets/Excel/Portia/PortiaConfig.xlsx
+++ b/Assets/Excel/Portia/PortiaConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamejam\ceshi\Assets\Excel\Portia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CF934F-D375-40F6-9999-B142CAD888F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5ED576-BCBE-478A-9805-966F52D8FB84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Machines" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="154">
   <si>
     <t>建筑唯一ID</t>
   </si>
@@ -63,9 +63,6 @@
     <t>itemTypeId</t>
   </si>
   <si>
-    <t>矿泉水</t>
-  </si>
-  <si>
     <t>配方唯一ID</t>
   </si>
   <si>
@@ -433,57 +430,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_Axe.png</t>
-  </si>
-  <si>
-    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_hoe_steel</t>
-  </si>
-  <si>
-    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_huYangMu</t>
-  </si>
-  <si>
-    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_stone_009</t>
-  </si>
-  <si>
-    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_stone_007</t>
-  </si>
-  <si>
-    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_crystal</t>
-  </si>
-  <si>
-    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_stone_011</t>
-  </si>
-  <si>
-    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_mushroom01</t>
-  </si>
-  <si>
-    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_machine_furnace02</t>
-  </si>
-  <si>
-    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_machine_sawing</t>
-  </si>
-  <si>
-    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_machine_cookingBench</t>
-  </si>
-  <si>
-    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_stone_002</t>
-  </si>
-  <si>
-    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_productionLine_WoodCompositeBoard</t>
-  </si>
-  <si>
-    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_metal_004</t>
-  </si>
-  <si>
-    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_home_wateredFloor</t>
-  </si>
-  <si>
-    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_products_steelPan</t>
-  </si>
-  <si>
-    <t>Assets\Games\GameJam\assets\UI\sprites\packageItem_metal_006</t>
-  </si>
-  <si>
     <t>Assets\Games\GameJam\assets\Model\itemmall\comparegame\ItemCom_Axe.prefab</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -576,10 +522,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>40.968f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">-150.503f </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -588,11 +530,83 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>39.948f</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>-154.462f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>蚝油蘑菇</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>出售价格</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>38.948f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>40.568f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_Axe.png</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_hoe_steel</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_huYangMu</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_stone_009</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_stone_007</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_crystal</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_mushroom01</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_machine_furnace02</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_machine_sawing</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_machine_cookingBench</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_stone_002</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_productionLine_WoodCompositeBoard</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_metal_004</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_home_wateredFloor</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_products_steelPan</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_metal_006</t>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_stone_011</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets\Games\GameJam\assets\UI\sprites\package\Item_small_HaoYouShuangGu</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1613,34 +1627,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" t="s">
-        <v>23</v>
-      </c>
       <c r="J1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -1648,34 +1662,34 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>27</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>28</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>29</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>30</v>
       </c>
-      <c r="I2" t="s">
-        <v>31</v>
-      </c>
       <c r="J2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -1683,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1710,7 +1724,7 @@
         <v>401</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -1718,7 +1732,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1745,7 +1759,7 @@
         <v>402</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -1753,7 +1767,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1777,7 +1791,7 @@
         <v>403</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -1785,7 +1799,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1809,7 +1823,7 @@
         <v>404</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1822,6 +1836,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="87.75" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1831,19 +1848,22 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" t="s">
         <v>45</v>
       </c>
-      <c r="D1" t="s">
-        <v>46</v>
-      </c>
       <c r="E1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G1" t="s">
-        <v>97</v>
+        <v>96</v>
+      </c>
+      <c r="H1" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -1854,19 +1874,22 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
         <v>36</v>
       </c>
-      <c r="D2" t="s">
-        <v>37</v>
-      </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G2" t="s">
         <v>103</v>
       </c>
-      <c r="G2" t="s">
-        <v>104</v>
+      <c r="H2" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1874,16 +1897,19 @@
         <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>123</v>
+        <v>105</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -1892,16 +1918,19 @@
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>124</v>
+        <v>106</v>
+      </c>
+      <c r="H4">
+        <v>20</v>
       </c>
       <c r="J4" s="3"/>
     </row>
@@ -1910,13 +1939,16 @@
         <v>201</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>108</v>
+        <v>138</v>
+      </c>
+      <c r="H5">
+        <v>30</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -1925,13 +1957,16 @@
         <v>202</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>109</v>
+        <v>139</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -1940,13 +1975,16 @@
         <v>203</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>110</v>
+        <v>140</v>
+      </c>
+      <c r="H7">
+        <v>20</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -1955,13 +1993,16 @@
         <v>204</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8">
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>111</v>
+        <v>141</v>
+      </c>
+      <c r="H8">
+        <v>30</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -1970,13 +2011,16 @@
         <v>205</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>112</v>
+        <v>152</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -1985,13 +2029,19 @@
         <v>301</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>131</v>
       </c>
       <c r="D10">
         <v>10</v>
       </c>
       <c r="E10">
         <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H10">
+        <v>20</v>
       </c>
       <c r="J10" s="4"/>
     </row>
@@ -2000,7 +2050,7 @@
         <v>302</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -2009,7 +2059,10 @@
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>113</v>
+        <v>142</v>
+      </c>
+      <c r="H11">
+        <v>30</v>
       </c>
       <c r="J11" s="3"/>
     </row>
@@ -2018,13 +2071,16 @@
         <v>401</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E12">
         <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>132</v>
+        <v>114</v>
+      </c>
+      <c r="H12">
+        <v>10</v>
       </c>
       <c r="J12" s="4"/>
     </row>
@@ -2033,13 +2089,16 @@
         <v>402</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13">
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>114</v>
+        <v>143</v>
+      </c>
+      <c r="H13">
+        <v>20</v>
       </c>
       <c r="J13" s="3"/>
     </row>
@@ -2048,13 +2107,16 @@
         <v>403</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14">
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>115</v>
+        <v>144</v>
+      </c>
+      <c r="H14">
+        <v>30</v>
       </c>
       <c r="J14" s="3"/>
     </row>
@@ -2063,13 +2125,16 @@
         <v>404</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E15">
         <v>4</v>
       </c>
       <c r="F15" t="s">
-        <v>116</v>
+        <v>145</v>
+      </c>
+      <c r="H15">
+        <v>10</v>
       </c>
       <c r="J15" s="3"/>
     </row>
@@ -2078,13 +2143,16 @@
         <v>501</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>117</v>
+        <v>146</v>
+      </c>
+      <c r="H16">
+        <v>20</v>
       </c>
       <c r="J16" s="3"/>
     </row>
@@ -2093,13 +2161,16 @@
         <v>502</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>118</v>
+        <v>147</v>
+      </c>
+      <c r="H17">
+        <v>30</v>
       </c>
       <c r="J17" s="3"/>
     </row>
@@ -2108,13 +2179,16 @@
         <v>503</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>119</v>
+        <v>148</v>
+      </c>
+      <c r="H18">
+        <v>10</v>
       </c>
       <c r="J18" s="3"/>
     </row>
@@ -2123,13 +2197,16 @@
         <v>505</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19" t="s">
-        <v>120</v>
+        <v>149</v>
+      </c>
+      <c r="H19">
+        <v>20</v>
       </c>
       <c r="J19" s="3"/>
     </row>
@@ -2138,13 +2215,16 @@
         <v>506</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20" t="s">
-        <v>121</v>
+        <v>150</v>
+      </c>
+      <c r="H20">
+        <v>30</v>
       </c>
       <c r="J20" s="3"/>
     </row>
@@ -2153,13 +2233,16 @@
         <v>507</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21" t="s">
-        <v>122</v>
+        <v>151</v>
+      </c>
+      <c r="H21">
+        <v>30</v>
       </c>
       <c r="J21" s="3"/>
     </row>
@@ -2171,7 +2254,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.75" bestFit="1" customWidth="1"/>
@@ -2184,54 +2267,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" t="s">
-        <v>13</v>
-      </c>
       <c r="G1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
       <c r="G2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" t="s">
         <v>57</v>
-      </c>
-      <c r="H2" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -2239,7 +2322,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>202</v>
@@ -2265,7 +2348,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4">
         <v>201</v>
@@ -2291,7 +2374,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5">
         <v>203</v>
@@ -2317,7 +2400,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>503</v>
@@ -2343,13 +2426,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1">
         <v>201202</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7">
         <v>402</v>
@@ -2369,13 +2452,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" t="s">
         <v>55</v>
-      </c>
-      <c r="D8" t="s">
-        <v>56</v>
       </c>
       <c r="E8">
         <v>403</v>
@@ -2395,7 +2478,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C9">
         <v>503</v>
@@ -2421,13 +2504,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" s="1">
         <v>203205</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E10">
         <v>507</v>
@@ -2447,13 +2530,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C11" s="1">
         <v>506501202</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E11">
         <v>404</v>
@@ -2466,6 +2549,32 @@
       </c>
       <c r="H11">
         <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="1">
+        <v>302</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>301</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2481,66 +2590,66 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" t="s">
         <v>69</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>70</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" t="s">
         <v>71</v>
       </c>
-      <c r="G1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" t="s">
-        <v>72</v>
-      </c>
       <c r="I1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" t="s">
         <v>67</v>
       </c>
-      <c r="D2" t="s">
-        <v>68</v>
-      </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" t="s">
         <v>73</v>
       </c>
-      <c r="G2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H2" t="s">
-        <v>74</v>
-      </c>
       <c r="I2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -2548,7 +2657,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C3">
         <v>101</v>
@@ -2569,7 +2678,7 @@
         <v>100</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -2577,7 +2686,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4">
         <v>102</v>
@@ -2595,10 +2704,10 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -2606,7 +2715,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5">
         <v>102</v>
@@ -2624,10 +2733,10 @@
         <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -2635,7 +2744,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -2653,7 +2762,7 @@
         <v>100</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -2661,7 +2770,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2679,7 +2788,7 @@
         <v>100</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -2687,7 +2796,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2705,7 +2814,7 @@
         <v>100</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2721,41 +2830,41 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" t="s">
         <v>87</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>88</v>
       </c>
-      <c r="C1" t="s">
-        <v>89</v>
-      </c>
       <c r="D1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" t="s">
         <v>90</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>91</v>
       </c>
-      <c r="C2" t="s">
-        <v>92</v>
-      </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2763,13 +2872,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -2777,13 +2886,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -2791,13 +2900,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -2805,13 +2914,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -2819,13 +2928,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="B8" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="D8">
         <v>6</v>
